--- a/xls/square_16_quad4_22.xlsx
+++ b/xls/square_16_quad4_22.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20">
+        <v>529</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20">
+        <v>289</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20">
+        <v>441</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20">
+        <v>1200</v>
+      </c>
+      <c r="I20">
+        <v>-0.4741096322511564</v>
+      </c>
+      <c r="J20">
+        <v>-1.2978469597425217</v>
+      </c>
+      <c r="K20">
+        <v>2.0957515099374273</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21">
+        <v>529</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21">
+        <v>289</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21">
+        <v>484</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21">
+        <v>1323</v>
+      </c>
+      <c r="I21">
+        <v>-1.091005688532911</v>
+      </c>
+      <c r="J21">
+        <v>-1.475312276489182</v>
+      </c>
+      <c r="K21">
+        <v>2.439985343751621</v>
+      </c>
+    </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
         <v>11</v>
@@ -482,13 +552,13 @@
         <v>1452</v>
       </c>
       <c r="I22">
-        <v>-0.8701830305274211</v>
+        <v>-1.2011615592336775</v>
       </c>
       <c r="J22">
-        <v>-1.757456154554961</v>
+        <v>-1.297365348336182</v>
       </c>
       <c r="K22">
-        <v>1.8634759636203493</v>
+        <v>3.3510430182526787</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -517,13 +587,13 @@
         <v>1587</v>
       </c>
       <c r="I23">
-        <v>-1.6051727928041644</v>
+        <v>-1.169785897744555</v>
       </c>
       <c r="J23">
-        <v>-1.5894461947607748</v>
+        <v>-1.172593261072361</v>
       </c>
       <c r="K23">
-        <v>1.8631845050566473</v>
+        <v>4.47882538623386</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -552,13 +622,13 @@
         <v>1728</v>
       </c>
       <c r="I24">
-        <v>-1.5334865352017908</v>
+        <v>-1.0039584478913248</v>
       </c>
       <c r="J24">
-        <v>-1.4734510901465543</v>
+        <v>-0.9153269504505115</v>
       </c>
       <c r="K24">
-        <v>2.772867271652375</v>
+        <v>4.708039669863913</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -587,13 +657,13 @@
         <v>1875</v>
       </c>
       <c r="I25">
-        <v>-1.1202676000186598</v>
+        <v>-0.11078577599921588</v>
       </c>
       <c r="J25">
-        <v>-0.799980776447357</v>
+        <v>-0.0921218334306117</v>
       </c>
       <c r="K25">
-        <v>3.524947304982301</v>
+        <v>4.751777549713064</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -622,13 +692,13 @@
         <v>2028</v>
       </c>
       <c r="I26">
-        <v>-0.9967406163807272</v>
+        <v>-0.01291277276995343</v>
       </c>
       <c r="J26">
-        <v>-0.7448278241804901</v>
+        <v>-0.012015143913069041</v>
       </c>
       <c r="K26">
-        <v>3.766859558955087</v>
+        <v>4.422287025304906</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -657,13 +727,13 @@
         <v>2187</v>
       </c>
       <c r="I27">
-        <v>-0.014355631724049033</v>
+        <v>-0.0001284176888645122</v>
       </c>
       <c r="J27">
-        <v>-0.013991710832424205</v>
+        <v>-0.00012746162351891398</v>
       </c>
       <c r="K27">
-        <v>3.430308414270371</v>
+        <v>3.5026348442099033</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -692,13 +762,13 @@
         <v>2352</v>
       </c>
       <c r="I28">
-        <v>-0.00456237217096618</v>
+        <v>-3.599030254331909e-5</v>
       </c>
       <c r="J28">
-        <v>-0.004637475178792008</v>
+        <v>-3.703256872021136e-5</v>
       </c>
       <c r="K28">
-        <v>3.2831458568382437</v>
+        <v>3.238430292716865</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -727,13 +797,13 @@
         <v>2523</v>
       </c>
       <c r="I29">
-        <v>-0.004138217436216684</v>
+        <v>-2.078724670675779e-5</v>
       </c>
       <c r="J29">
-        <v>-0.004465086925932954</v>
+        <v>-2.246739907398814e-5</v>
       </c>
       <c r="K29">
-        <v>3.288251378352647</v>
+        <v>3.1211830115146406</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -762,13 +832,13 @@
         <v>2700</v>
       </c>
       <c r="I30">
-        <v>-0.0008811417882357926</v>
+        <v>-6.336449297334907e-6</v>
       </c>
       <c r="J30">
-        <v>-0.0009510079058961803</v>
+        <v>-6.8594379071670505e-6</v>
       </c>
       <c r="K30">
-        <v>2.98356381293101</v>
+        <v>2.868077380275467</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -797,13 +867,13 @@
         <v>2883</v>
       </c>
       <c r="I31">
-        <v>-0.002726510148394246</v>
+        <v>-1.1299838285359683e-5</v>
       </c>
       <c r="J31">
-        <v>-0.0031117389740780016</v>
+        <v>-1.281706301133873e-5</v>
       </c>
       <c r="K31">
-        <v>3.2210505385689867</v>
+        <v>2.9949239198975266</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -832,13 +902,13 @@
         <v>3072</v>
       </c>
       <c r="I32">
-        <v>-0.0005457181743278463</v>
+        <v>-3.113363978384069e-6</v>
       </c>
       <c r="J32">
-        <v>-0.0005966474821752388</v>
+        <v>-3.4124205163992338e-6</v>
       </c>
       <c r="K32">
-        <v>2.883700122338683</v>
+        <v>2.7087957594107532</v>
       </c>
     </row>
   </sheetData>
